--- a/docs/eu/0.0.1/StructureDefinition-ImComposition.xlsx
+++ b/docs/eu/0.0.1/StructureDefinition-ImComposition.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.eu/fhir/StructureDefinition/CompositionEu|0.1.0-ballot</t>
+    <t>https://hl7.lt/fhir/eu/StructureDefinition/CompositionEu|0.1.0-ballot</t>
   </si>
   <si>
     <t>Abstract</t>

--- a/docs/eu/0.0.1/StructureDefinition-ImComposition.xlsx
+++ b/docs/eu/0.0.1/StructureDefinition-ImComposition.xlsx
@@ -506,7 +506,7 @@
     <t>informationRecipient</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.eu/fhir/StructureDefinition/information-recipient|0.1.1}
+    <t xml:space="preserve">Extension {http://hl7.eu/fhir/StructureDefinition/information-recipient|1.2.0}
 </t>
   </si>
   <si>
